--- a/Unificar/roster.xlsx
+++ b/Unificar/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Elencos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Unificar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1035" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D00F3CEC-CF0D-4880-89C8-9BC61D1DBB03}"/>
+  <xr:revisionPtr revIDLastSave="1187" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98A9FAAB-79FD-4040-A383-BC3CF6F16627}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="1" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="fines" sheetId="11" r:id="rId7"/>
     <sheet name="transactions" sheetId="12" r:id="rId8"/>
     <sheet name="transaction_items" sheetId="13" r:id="rId9"/>
+    <sheet name="games" sheetId="14" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">players!$A$1:$K$407</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="519">
   <si>
     <t>player_id</t>
   </si>
@@ -1544,6 +1545,69 @@
   </si>
   <si>
     <t>roster_order</t>
+  </si>
+  <si>
+    <t>id_jogo</t>
+  </si>
+  <si>
+    <t>id_time_1</t>
+  </si>
+  <si>
+    <t>nome_time_1</t>
+  </si>
+  <si>
+    <t>pontos_time_1</t>
+  </si>
+  <si>
+    <t>pontos_time_2</t>
+  </si>
+  <si>
+    <t>id_time_2</t>
+  </si>
+  <si>
+    <t>nome_time_2</t>
+  </si>
+  <si>
+    <t>J1R1S2526</t>
+  </si>
+  <si>
+    <t>J2R1S2526</t>
+  </si>
+  <si>
+    <t>J3R1S2526</t>
+  </si>
+  <si>
+    <t>J4R1S2526</t>
+  </si>
+  <si>
+    <t>J5R1S2526</t>
+  </si>
+  <si>
+    <t>J6R1S2526</t>
+  </si>
+  <si>
+    <t>J7R1S2526</t>
+  </si>
+  <si>
+    <t>J1R2S2526</t>
+  </si>
+  <si>
+    <t>J2R2S2526</t>
+  </si>
+  <si>
+    <t>J3R2S2526</t>
+  </si>
+  <si>
+    <t>J4R2S2526</t>
+  </si>
+  <si>
+    <t>J5R2S2526</t>
+  </si>
+  <si>
+    <t>J6R2S2526</t>
+  </si>
+  <si>
+    <t>J7R2S2526</t>
   </si>
 </sst>
 </file>
@@ -15335,6 +15399,398 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C74861F-411E-43E0-91B2-C73D752B81C9}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2">
+        <v>14</v>
+      </c>
+      <c r="C2" t="str">
+        <f>VLOOKUP(B2,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2" t="str">
+        <f>VLOOKUP(F2,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3" t="str">
+        <f>VLOOKUP(B3,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="str">
+        <f>VLOOKUP(F3,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4" t="str">
+        <f>VLOOKUP(B4,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="str">
+        <f>VLOOKUP(F4,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5" t="str">
+        <f>VLOOKUP(B5,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="str">
+        <f>VLOOKUP(F5,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>509</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="str">
+        <f>VLOOKUP(B6,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6" t="str">
+        <f>VLOOKUP(F6,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>510</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7" t="str">
+        <f>VLOOKUP(B7,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7" t="str">
+        <f>VLOOKUP(F7,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="str">
+        <f>VLOOKUP(B8,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8" t="str">
+        <f>VLOOKUP(F8,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>512</v>
+      </c>
+      <c r="B9">
+        <v>14</v>
+      </c>
+      <c r="C9" t="str">
+        <f>VLOOKUP(B9,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9" t="str">
+        <f>VLOOKUP(F9,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>513</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="str">
+        <f>VLOOKUP(B10,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10" t="str">
+        <f>VLOOKUP(F10,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>514</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="str">
+        <f>VLOOKUP(B11,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <f>VLOOKUP(F11,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="str">
+        <f>VLOOKUP(B12,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12" t="str">
+        <f>VLOOKUP(F12,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>516</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="str">
+        <f>VLOOKUP(B13,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="str">
+        <f>VLOOKUP(F13,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>517</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="str">
+        <f>VLOOKUP(B14,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>12</v>
+      </c>
+      <c r="G14" t="str">
+        <f>VLOOKUP(F14,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>518</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15" t="str">
+        <f>VLOOKUP(B15,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>11</v>
+      </c>
+      <c r="G15" t="str">
+        <f>VLOOKUP(F15,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7488F4-E8E1-402F-983B-65418E8B7580}">
   <dimension ref="A1:K15"/>
@@ -16704,13 +17160,13 @@
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" style="2" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17023,6 +17479,15 @@
       <c r="C16">
         <v>1</v>
       </c>
+      <c r="D16" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H16" s="2">
+        <v>3100000</v>
+      </c>
       <c r="L16" t="str">
         <f>VLOOKUP(B16,players!A:B,2)</f>
         <v>Jaden Ivey</v>
@@ -17053,6 +17518,21 @@
       <c r="C18">
         <v>3</v>
       </c>
+      <c r="D18" s="2">
+        <v>7500000</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8500000</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H18" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="L18" t="str">
         <f>VLOOKUP(B18,players!A:B,2)</f>
         <v>Ace Bailey</v>
@@ -17098,6 +17578,21 @@
       <c r="C21">
         <v>6</v>
       </c>
+      <c r="D21" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="L21" t="str">
         <f>VLOOKUP(B21,players!A:B,2)</f>
         <v>Asa Newell</v>
@@ -17128,6 +17623,15 @@
       <c r="C23">
         <v>8</v>
       </c>
+      <c r="D23" s="2">
+        <v>4200000</v>
+      </c>
+      <c r="F23" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="L23" t="str">
         <f>VLOOKUP(B23,players!A:B,2)</f>
         <v>Matas Buzelis</v>
@@ -17143,6 +17647,15 @@
       <c r="C24">
         <v>9</v>
       </c>
+      <c r="D24" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F24" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H24" s="2">
+        <v>40000000</v>
+      </c>
       <c r="L24" t="str">
         <f>VLOOKUP(B24,players!A:B,2)</f>
         <v>Anthony Edwards</v>
@@ -17158,6 +17671,15 @@
       <c r="C25">
         <v>10</v>
       </c>
+      <c r="D25" s="2">
+        <v>30500000</v>
+      </c>
+      <c r="F25" s="2">
+        <v>30500000</v>
+      </c>
+      <c r="H25" s="2">
+        <v>30500000</v>
+      </c>
       <c r="L25" t="str">
         <f>VLOOKUP(B25,players!A:B,2)</f>
         <v>Tyrese Maxey</v>
@@ -17173,6 +17695,9 @@
       <c r="C26">
         <v>11</v>
       </c>
+      <c r="D26" s="2">
+        <v>1000000</v>
+      </c>
       <c r="L26" t="str">
         <f>VLOOKUP(B26,players!A:B,2)</f>
         <v>Donte DiVincenzo</v>
@@ -17187,6 +17712,9 @@
       </c>
       <c r="C27">
         <v>12</v>
+      </c>
+      <c r="D27" s="2">
+        <v>7000000</v>
       </c>
       <c r="L27" t="str">
         <f>VLOOKUP(B27,players!A:B,2)</f>
@@ -19263,6 +19791,7 @@
     <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -19413,7 +19942,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -19423,15 +19952,21 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2">
-        <v>9000000</v>
-      </c>
-      <c r="G6" s="2" t="s">
+        <v>4500000</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="J6" s="2">
+        <v>5500000</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
